--- a/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="92">
   <si>
     <t>DY</t>
   </si>
@@ -656,558 +656,571 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AQ102"/>
+  <dimension ref="A5:AR102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E7" s="2">
         <v>46144</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46053</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45955</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45864</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45773</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45682</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45591</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45500</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45409</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45318</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45227</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45136</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45045</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44954</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44863</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44772</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44681</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44590</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44499</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44408</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44317</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44226</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44128</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44037</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43946</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43855</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43764</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43673</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43582</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43491</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43400</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43309</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43218</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43127</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43036</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42945</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42854</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42763</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42672</v>
       </c>
-      <c r="AQ7" s="2">
+      <c r="AR7" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2005900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1964800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1457600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1451800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1377900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1258600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1084500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1272000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1203100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1142400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>952500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1136100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1041500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1045500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>917500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1042400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>972300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>876300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>761500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>854000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>787600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>727500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>750700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>810300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>823900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>814300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>737600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>884100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>884200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>833700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>748600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>848200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>799500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>731400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>655100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>756200</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>780200</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>786300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>701100</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>799200</v>
       </c>
-      <c r="AQ8" s="3">
+      <c r="AR8" s="3">
         <v>789200</v>
       </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1565400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1578100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1192600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1131600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1070500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1011100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>887900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1007400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>952900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>921600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>791400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>886700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>830400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>853400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>765700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>850900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>798000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>745700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>656600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>705900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>651400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>620000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>645500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>658400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>658000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>680200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>633200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>724400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>720400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>701800</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>633300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>687200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>642400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>599600</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>540600</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>600800</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>606900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>621500</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>561400</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>615000</v>
       </c>
-      <c r="AQ9" s="3">
+      <c r="AR9" s="3">
         <v>605900</v>
       </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>440600</v>
+      </c>
+      <c r="E10" s="3">
         <v>386700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>264900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>320200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>307500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>247500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>196600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>264600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>250200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>220800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>161100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>249400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>211100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>192100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>151800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>191500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>174300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>130600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>104900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>148100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>136200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>107500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>105200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>151900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>165900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>134100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>104400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>159700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>163800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>131900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>115300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>161000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>157100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>131800</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>114500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>155400</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>173300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>164800</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>139700</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>184200</v>
       </c>
-      <c r="AQ10" s="3">
+      <c r="AR10" s="3">
         <v>183300</v>
       </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1251,8 +1264,9 @@
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
       <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1376,8 +1390,11 @@
       <c r="AQ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AR12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1501,58 +1518,61 @@
       <c r="AQ13" s="3">
         <v>0</v>
       </c>
+      <c r="AR13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-2300</v>
+      </c>
+      <c r="E14" s="3">
         <v>-2000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>24000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-10100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-9800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-7200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-12400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-8400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-7600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1560,33 +1580,33 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>500</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>40800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>100</v>
       </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1599,8 +1619,8 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
-        <v>0</v>
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ14" s="3">
         <v>0</v>
@@ -1614,145 +1634,151 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
+      <c r="AN14" s="3">
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AP14" s="3">
-        <v>0</v>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AQ14" s="3">
         <v>0</v>
       </c>
+      <c r="AR14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E15" s="3">
         <v>111600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>88200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>62200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>60900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>58400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>54800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>46600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>45300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>42500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>38000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>37300</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>36700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>35500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>35300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>36600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>37300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>37800</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>38500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>39100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>43600</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>42300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>44100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>45900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>46600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>47400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>47200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>46300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>45900</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>45500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>44800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>43400</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>42400</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>42700</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>40200</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>37400</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>35700</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>34500</v>
       </c>
-      <c r="AQ15" s="3">
+      <c r="AR15" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1793,258 +1819,265 @@
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
       <c r="AQ16" s="3"/>
+      <c r="AR16" s="3"/>
     </row>
-    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1813900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1821000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1389700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1301100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1238100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1173200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1019500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1166000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1099000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1061400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>909700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1016700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>953200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>973000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>874400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>965100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>906700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>851700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>757800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>810500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>754600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>726200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>753000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>763300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>769900</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>832700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>740900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>841600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>832700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>806700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>752700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>801500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>751700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>705200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>643400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>708100</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>706700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>720200</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>655300</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>709700</v>
       </c>
-      <c r="AQ17" s="3">
+      <c r="AR17" s="3">
         <v>704100</v>
       </c>
     </row>
-    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>192000</v>
+      </c>
+      <c r="E18" s="3">
         <v>143800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>67900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>150700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>139800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>85400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>65100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>106000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>104000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>81000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>42800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>119400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>88300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>72500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>43100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>77300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>65600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>3700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>43500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>33000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>1300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>47000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>54000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-18400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>42500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>51500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>27000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>46700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>47800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>26200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>11700</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>48100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>73500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>66100</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>45800</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>89500</v>
       </c>
-      <c r="AQ18" s="3">
+      <c r="AR18" s="3">
         <v>85100</v>
       </c>
     </row>
-    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2088,633 +2121,649 @@
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
       <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
     </row>
-    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E20" s="3">
         <v>3500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>2900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>3200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>1800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>2700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>1400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>5700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>1200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>7700</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>5900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>6000</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>4800</v>
-      </c>
-      <c r="AO20" s="3">
-        <v>1000</v>
       </c>
       <c r="AP20" s="3">
         <v>1000</v>
       </c>
       <c r="AQ20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="AR20" s="3">
         <v>3500</v>
       </c>
     </row>
-    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>305200</v>
+      </c>
+      <c r="E21" s="3">
         <v>251900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>153200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>211400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>197400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>141300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>118800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>156700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>148900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>123100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>87500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>160500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>124500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>106900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>80200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>115200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>103500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>66000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>41200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>81800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>72500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>43100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>42000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>93000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>101300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>28600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>43900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>91300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>102700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>79100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>43000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>95100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>96700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>77200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>54400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>96700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>119800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>108300</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>82600</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>125000</v>
       </c>
-      <c r="AQ21" s="3">
+      <c r="AR21" s="3">
         <v>124700</v>
       </c>
     </row>
-    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E22" s="3">
         <v>35500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>23100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>13800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>15600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>16100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>14000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>11600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>10600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>9300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9300</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>5900</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>4700</v>
       </c>
       <c r="Z22" s="3">
         <v>4700</v>
       </c>
       <c r="AA22" s="3">
+        <v>4700</v>
+      </c>
+      <c r="AB22" s="3">
         <v>7900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12600</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>13100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>12900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>12200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>12400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>11300</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>10400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>10200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9900</v>
-      </c>
-      <c r="AL22" s="3">
-        <v>9700</v>
       </c>
       <c r="AM22" s="3">
         <v>9700</v>
       </c>
       <c r="AN22" s="3">
+        <v>9700</v>
+      </c>
+      <c r="AO22" s="3">
         <v>9400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>9200</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>9100</v>
       </c>
-      <c r="AQ22" s="3">
+      <c r="AR22" s="3">
         <v>9700</v>
       </c>
     </row>
-    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>154000</v>
+      </c>
+      <c r="E23" s="3">
         <v>106700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>17900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>140300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>131100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>78600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>44200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>91300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>77400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>112400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>81800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>66100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>31900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>69200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>58900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-4900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>34900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>46000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>49300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-29700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-15300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>30800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>42600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>20500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>38300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>41400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>23700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>44400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>69800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>61500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>37700</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>81400</v>
       </c>
-      <c r="AQ23" s="3">
+      <c r="AR23" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>38300</v>
+      </c>
+      <c r="E24" s="3">
         <v>15400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>33900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>33600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>17600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>11600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>21500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>21500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>14600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>7100</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>15100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>15000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-5700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>6200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>6500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>12000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>12200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>2700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-5200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>12700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>10500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>11500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-5700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>15600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>26100</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>22800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>14000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>30300</v>
       </c>
-      <c r="AQ24" s="3">
+      <c r="AR24" s="3">
         <v>29600</v>
       </c>
     </row>
-    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2838,258 +2887,267 @@
       <c r="AQ25" s="3">
         <v>0</v>
       </c>
+      <c r="AR25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E26" s="3">
         <v>91300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>16300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>106400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>97500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>61000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>32700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>69800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>68400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>62600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>83700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>60200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>51500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>24800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>54000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>43900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>19500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>28700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>18200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>33900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>37000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-32400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>24200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>29900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>14300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>27800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>17200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>7900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>28800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>43700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>38800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>23700</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>51100</v>
       </c>
-      <c r="AQ26" s="3">
+      <c r="AR26" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E27" s="3">
         <v>91300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>106400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>97500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>61000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>32700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>69800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>68400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>62600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>83700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>60200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>51500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>24800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>54000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>43900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>19500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>28700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>33900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>37000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-32400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-10100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>24200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>29900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>14300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>27800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>17200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>7900</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>28800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>43700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>38800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>23700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>51100</v>
       </c>
-      <c r="AQ27" s="3">
+      <c r="AR27" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3213,8 +3271,11 @@
       <c r="AQ28" s="3">
         <v>0</v>
       </c>
+      <c r="AR28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3263,8 +3324,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -3281,35 +3342,35 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>2600</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
+        <v>0</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3317,12 +3378,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>32200</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3338,8 +3399,11 @@
       <c r="AQ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AR29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3463,8 +3527,11 @@
       <c r="AQ30" s="3">
         <v>0</v>
       </c>
+      <c r="AR30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3588,258 +3655,267 @@
       <c r="AQ31" s="3">
         <v>0</v>
       </c>
+      <c r="AR31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-2900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-3200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-1800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-7700</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-5900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-4800</v>
-      </c>
-      <c r="AO32" s="3">
-        <v>-1000</v>
       </c>
       <c r="AP32" s="3">
         <v>-1000</v>
       </c>
       <c r="AQ32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="AR32" s="3">
         <v>-3500</v>
       </c>
     </row>
-    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E33" s="3">
         <v>91300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>106400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>97500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>61000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>32700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>69800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>68400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>62600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>83700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>60200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>51500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>24800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>54000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>43900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>19500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>28700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>33900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>37000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-32400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>24200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>29900</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>14300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>27800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>17200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>40100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>28800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>43700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>38800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>23700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>51100</v>
       </c>
-      <c r="AQ33" s="3">
+      <c r="AR33" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3963,263 +4039,272 @@
       <c r="AQ34" s="3">
         <v>0</v>
       </c>
+      <c r="AR34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E35" s="3">
         <v>91300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>106400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>97500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>61000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>32700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>69800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>68400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>62600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>83700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>60200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>51500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>24800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>54000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>43900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>19500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>28700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>33900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>37000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-32400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>24200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>29900</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>14300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>27800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>17200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>40100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>28800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>43700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>38800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>23700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>51100</v>
       </c>
-      <c r="AQ35" s="3">
+      <c r="AR35" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E38" s="2">
         <v>46144</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46053</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45955</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45864</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45773</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45682</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45591</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45500</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45409</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45318</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45227</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45136</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45045</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44954</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44863</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44772</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44681</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44590</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44499</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44408</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44317</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44226</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44128</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44037</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43946</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43855</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43764</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43673</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43582</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43491</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43400</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43309</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43218</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43127</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43036</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42945</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42854</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42763</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42672</v>
       </c>
-      <c r="AQ38" s="2">
+      <c r="AR38" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4263,8 +4348,9 @@
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
       <c r="AQ39" s="3"/>
+      <c r="AR39" s="3"/>
     </row>
-    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4308,178 +4394,182 @@
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
       <c r="AQ40" s="3"/>
+      <c r="AR40" s="3"/>
     </row>
-    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>340100</v>
+      </c>
+      <c r="E41" s="3">
         <v>538800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>709200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>110100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>28500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>92700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>15300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>19600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>26100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>101100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>15700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>83400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>71400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>224200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>65300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>120300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>185600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>310800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>263700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>261900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>330600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>11800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>12000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>22500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>643900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>54600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>11800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>12600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>33600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>128300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>21500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>23900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>57900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>84000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>24500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>38600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>19400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>29500</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>21700</v>
       </c>
-      <c r="AQ41" s="3">
+      <c r="AR41" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>11700</v>
+      </c>
+      <c r="E42" s="3">
         <v>10300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>11000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>10300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>8000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>10400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>11300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>15200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>22300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>20200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>22300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20400</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4558,258 +4648,267 @@
       <c r="AQ42" s="3">
         <v>0</v>
       </c>
+      <c r="AR42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2514900</v>
+      </c>
+      <c r="E43" s="3">
         <v>2239200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1879200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1755800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1744900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1631500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1441300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1723700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1588000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1442300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1298700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1535000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1303400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1243600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1114900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1297800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1170700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1043300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>933200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1077900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1102800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1048500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1057000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1144300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1156600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1145800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1073600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1262900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1156800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1001900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>844600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1003300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>863500</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>763100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>332600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>349600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>377300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>355100</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>335500</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>329800</v>
       </c>
-      <c r="AQ43" s="3">
+      <c r="AR43" s="3">
         <v>328000</v>
       </c>
     </row>
-    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E44" s="3">
         <v>143300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>128300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>120100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>122600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>133000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>127300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>116000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>101200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>104000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>108600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>114000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>117200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>115700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>115000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>107100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>98900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>94100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>81300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>69900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>69700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>71100</v>
-      </c>
-      <c r="Y44" s="3">
-        <v>70800</v>
       </c>
       <c r="Z44" s="3">
         <v>70800</v>
       </c>
       <c r="AA44" s="3">
+        <v>70800</v>
+      </c>
+      <c r="AB44" s="3">
         <v>77800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>92600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>98300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>104900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>107400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>105200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>94400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>90800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>87800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>84300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>448500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>490400</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>472500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>529100</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>481600</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>570000</v>
       </c>
-      <c r="AQ44" s="3">
+      <c r="AR44" s="3">
         <v>450600</v>
       </c>
     </row>
-    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4852,214 +4951,220 @@
       <c r="P45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="Q45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R45" s="3">
         <v>38600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>43900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>47000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>30900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>37500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>43300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>47900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>29000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>38400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>49700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>48600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>31800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>32300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>31100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>37800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>29100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>33300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>30100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>30800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>39700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>28800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>50100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>46700</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>41700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>45400</v>
       </c>
-      <c r="AQ45" s="3">
+      <c r="AR45" s="3">
         <v>38800</v>
       </c>
     </row>
-    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3052200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2970400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2756900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2026000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1938900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1824700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1694600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1896800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1760700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1626800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1550000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1708700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1555200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1483800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1492700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1513000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1433800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1370000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1356100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1449000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>1477700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>1498100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>1168600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>1265500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1306600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1930900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1258300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1411900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1307800</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1178500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1096400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1148900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1005300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>936100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>904800</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>893400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>938500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>950200</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>888300</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>966900</v>
       </c>
-      <c r="AQ46" s="3">
+      <c r="AR46" s="3">
         <v>851200</v>
       </c>
     </row>
-    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -5102,63 +5207,63 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R47" s="3">
         <v>8300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>12500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>15300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>16700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>16200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>17600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>18600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>19900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>21300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>22700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>24200</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>26200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>28400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>55200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>32000</v>
       </c>
-      <c r="AI47" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AJ47" s="3" t="s">
         <v>8</v>
       </c>
@@ -5183,258 +5288,267 @@
       <c r="AQ47" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AR47" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>834300</v>
+      </c>
+      <c r="E48" s="3">
         <v>767800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>745000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>686700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>676800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>679400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>654100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>622800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>563000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>538700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>521300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>505100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>466000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>447100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>435100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>403300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>377600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>361100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>355900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>346200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>343600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>340500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>337100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>354200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>385500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>422100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>446200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>463000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>491700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>498400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>424800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>428300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>423700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>416300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>414800</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>423300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>422100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>378400</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>344100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>337700</v>
       </c>
-      <c r="AQ48" s="3">
+      <c r="AR48" s="3">
         <v>326700</v>
       </c>
     </row>
-    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2534300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2324700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2369400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>572200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>582000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>538300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>550100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>560000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>429500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>423800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>420900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>425700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>352100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>355600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>359100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>362600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>366500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>370400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>374300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>378300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>382500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>387100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>391800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>397000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>402000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>407200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>465700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>470900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>476200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>481500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>486900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>492300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>498100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>503900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>493200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>499100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>505300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>513100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>498200</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>500300</v>
       </c>
-      <c r="AQ49" s="3">
+      <c r="AR49" s="3">
         <v>508000</v>
       </c>
     </row>
-    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5558,8 +5672,11 @@
       <c r="AQ50" s="3">
         <v>0</v>
       </c>
+      <c r="AR50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5683,133 +5800,139 @@
       <c r="AQ51" s="3">
         <v>0</v>
       </c>
+      <c r="AR51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>39200</v>
+      </c>
+      <c r="E52" s="3">
         <v>41700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>35600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>35900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>58000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>11800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>29800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>20700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>19000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>19500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>13900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>15000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>18000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>16800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>17500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>18100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>17900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>15800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>21400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>21100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>29000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>29700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>30600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>31400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>24800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>25500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>26400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>24400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>34200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>31700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>25400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>26800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>28200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>36800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>33400</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>34300</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>35800</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>33500</v>
       </c>
-      <c r="AQ52" s="3">
+      <c r="AR52" s="3">
         <v>33800</v>
       </c>
     </row>
-    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5933,133 +6056,139 @@
       <c r="AQ53" s="3">
         <v>0</v>
       </c>
+      <c r="AR53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6540000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6180400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5979200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3324800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3219900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3105000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2945400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3114700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2779400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2611600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2516900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2664200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>2395600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>2311700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>2313300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>2305300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2206400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>2132100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>2118200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>2204700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>2241900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>2263000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1944200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>2065100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>2144700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>2812900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2217600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2395600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2328400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2211200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2097500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2133200</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>1952400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>1883000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>1841000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>1852500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>1899300</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>1876000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>1766400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>1838400</v>
       </c>
-      <c r="AQ54" s="3">
+      <c r="AR54" s="3">
         <v>1719700</v>
       </c>
     </row>
-    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -6103,8 +6232,9 @@
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
       <c r="AQ55" s="3"/>
+      <c r="AR55" s="3"/>
     </row>
-    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6148,177 +6278,181 @@
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
       <c r="AQ56" s="3"/>
+      <c r="AR56" s="3"/>
     </row>
-    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>610000</v>
+      </c>
+      <c r="E57" s="3">
         <v>666600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>497300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>297100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>264900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>259200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>223500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>241000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>233500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>212900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>222100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>215300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>204800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>196200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>207700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>201000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>187600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>176400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>155900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>173600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>173200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>171000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>159000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>183700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>177300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>194400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>119600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>129500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>140300</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>138700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>119500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>134700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>125700</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>112200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>92400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>109900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>133000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>119300</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>99300</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>114700</v>
       </c>
-      <c r="AQ57" s="3">
+      <c r="AR57" s="3">
         <v>115500</v>
       </c>
     </row>
-    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>72000</v>
+      </c>
+      <c r="E58" s="3">
         <v>50800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>46300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>58100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>59200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>53200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>45800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>39800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>33300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>50400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>49500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>47600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>46800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>46100</v>
-      </c>
-      <c r="Q58" s="3">
-        <v>17500</v>
       </c>
       <c r="R58" s="3">
         <v>17500</v>
@@ -6333,22 +6467,22 @@
         <v>17500</v>
       </c>
       <c r="V58" s="3">
+        <v>17500</v>
+      </c>
+      <c r="W58" s="3">
         <v>13100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>66600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>61500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>81700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>78100</v>
-      </c>
-      <c r="AA58" s="3">
-        <v>22500</v>
       </c>
       <c r="AB58" s="3">
         <v>22500</v>
@@ -6360,546 +6494,561 @@
         <v>22500</v>
       </c>
       <c r="AE58" s="3">
+        <v>22500</v>
+      </c>
+      <c r="AF58" s="3">
         <v>16900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11300</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>5600</v>
       </c>
-      <c r="AH58" s="3">
-        <v>0</v>
-      </c>
       <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="3">
         <v>31300</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>28900</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>26500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>24100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>21700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>14400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>18800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>17500</v>
       </c>
-      <c r="AQ58" s="3">
+      <c r="AR58" s="3">
         <v>13100</v>
       </c>
     </row>
-    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>311500</v>
+      </c>
+      <c r="E59" s="3">
         <v>227500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>207200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>103500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>110800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>173600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>141700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>136900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>67600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>103600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>73700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>61700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>57400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>68100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>244300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>252600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>227100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>201700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>208400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>206400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>207600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>203500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>207800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>201900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>211500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>211400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>180900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>212800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>199800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>191700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>159900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>169300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>153300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>134800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>140800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>149200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>163900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>155100</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>145000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>179700</v>
       </c>
-      <c r="AQ59" s="3">
+      <c r="AR59" s="3">
         <v>194000</v>
       </c>
     </row>
-    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1299900</v>
+      </c>
+      <c r="E60" s="3">
         <v>1149400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1006900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>656500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>612700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>631800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>587200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>608500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>511100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>513600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>506300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>488800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>459400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>433100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>469600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>471100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>432100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>395700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>381800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>393200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>447500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>436100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>448500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>463700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>411300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>428300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>323000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>364800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>357000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>341700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>285000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>304000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>310300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>275900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>259600</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>283100</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>318500</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>288900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>263200</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>312000</v>
       </c>
-      <c r="AQ60" s="3">
+      <c r="AR60" s="3">
         <v>322600</v>
       </c>
     </row>
-    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2976400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2948200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2945700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1006500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1087600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1092500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1010100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1165700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>988600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>889500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>835500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>993300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>842600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>846900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>807400</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>811400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>815300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>819300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>823300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>827200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>831200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>835200</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>501600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>490000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>665500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1363900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>844400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>970200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>932300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>867400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>867600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>867800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>727300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>731700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>733800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>736000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>738300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>811600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>740600</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>774500</v>
       </c>
-      <c r="AQ61" s="3">
+      <c r="AR61" s="3">
         <v>706200</v>
       </c>
     </row>
-    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>95000</v>
+      </c>
+      <c r="E62" s="3">
         <v>90700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>93500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>82200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>82400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>76800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>75100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>77300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>76200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>70800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>70200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>68300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>72100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>167600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>164200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>161900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>158800</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>154600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>173500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>182700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>181800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>182800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>198200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>194100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>186800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>181600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>180400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>185700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>181000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>140800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>144500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>131500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>128400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>122500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>143800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>170900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>152800</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>147600</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>138200</v>
       </c>
-      <c r="AQ62" s="3">
+      <c r="AR62" s="3">
         <v>133600</v>
       </c>
     </row>
-    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -7023,8 +7172,11 @@
       <c r="AQ63" s="3">
         <v>0</v>
       </c>
+      <c r="AR63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -7148,8 +7300,11 @@
       <c r="AQ64" s="3">
         <v>0</v>
       </c>
+      <c r="AR64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7273,133 +7428,139 @@
       <c r="AQ65" s="3">
         <v>0</v>
       </c>
+      <c r="AR65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>4476100</v>
+      </c>
+      <c r="E66" s="3">
         <v>4284700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4120000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1841500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1850200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1838800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1706300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1881000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1620900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1531000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1462200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1610200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1431600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1414300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1444500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1446700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1409400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1373800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1359700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1393900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1461400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1453100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1132900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>1151900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>1270900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>1979000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1349000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1515400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1474900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1390000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1293300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1316400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1169200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>1136000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>1116000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>1162900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>1227700</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>1253300</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>1151400</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>1224700</v>
       </c>
-      <c r="AQ66" s="3">
+      <c r="AR66" s="3">
         <v>1162400</v>
       </c>
     </row>
-    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7443,8 +7604,9 @@
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
       <c r="AQ67" s="3"/>
+      <c r="AR67" s="3"/>
     </row>
-    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7568,8 +7730,11 @@
       <c r="AQ68" s="3">
         <v>0</v>
       </c>
+      <c r="AR68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7693,8 +7858,11 @@
       <c r="AQ69" s="3">
         <v>0</v>
       </c>
+      <c r="AR69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7818,8 +7986,11 @@
       <c r="AQ70" s="3">
         <v>0</v>
       </c>
+      <c r="AR70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7943,133 +8114,139 @@
       <c r="AQ71" s="3">
         <v>0</v>
       </c>
+      <c r="AR71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1674400</v>
+      </c>
+      <c r="E72" s="3">
         <v>1558800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1467500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1451300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1344900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>1247400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>1220400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>1201300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1131500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1063100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>1040300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1026600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>942800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>882600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>855100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>838300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>784300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>747100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>748400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>798500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>769800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>797700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>800600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>867800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>833800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>796800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>829700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>840900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>816700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>786800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>772500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>784500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>756700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>726800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>709600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>674200</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>652300</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>608600</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>600500</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>588900</v>
       </c>
-      <c r="AQ72" s="3">
+      <c r="AR72" s="3">
         <v>537900</v>
       </c>
     </row>
-    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8193,8 +8370,11 @@
       <c r="AQ73" s="3">
         <v>0</v>
       </c>
+      <c r="AR73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8318,8 +8498,11 @@
       <c r="AQ74" s="3">
         <v>0</v>
       </c>
+      <c r="AR74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8443,133 +8626,139 @@
       <c r="AQ75" s="3">
         <v>0</v>
       </c>
+      <c r="AR75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>2063900</v>
+      </c>
+      <c r="E76" s="3">
         <v>1895700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1859100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1483300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1369700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1266200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1239100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1233700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1158400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1080600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1054700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1053900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>964000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>897400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>868800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>858600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>797000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>758300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>758500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>810800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>780400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>810000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>811300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>913100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>873700</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>833900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>868600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>880200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>853400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>821200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>804200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>816900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>783200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>747000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>725000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>689600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>671600</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>622700</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>615100</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>613700</v>
       </c>
-      <c r="AQ76" s="3">
+      <c r="AR76" s="3">
         <v>557300</v>
       </c>
     </row>
-    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8693,263 +8882,272 @@
       <c r="AQ77" s="3">
         <v>0</v>
       </c>
+      <c r="AR77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:44" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:44" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46235</v>
+      </c>
+      <c r="E80" s="2">
         <v>46144</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46053</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45955</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45864</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45773</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45682</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45591</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45500</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45409</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45318</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45227</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45136</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45045</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44954</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44863</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44772</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44681</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44590</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44499</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44408</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44317</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44226</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44128</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44037</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43946</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43855</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43764</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43673</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43582</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43491</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43400</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43309</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43218</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43127</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43036</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42945</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42854</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42763</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42672</v>
       </c>
-      <c r="AQ80" s="2">
+      <c r="AR80" s="2">
         <v>42581</v>
       </c>
     </row>
-    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>115600</v>
+      </c>
+      <c r="E81" s="3">
         <v>91300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>106400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>97500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>61000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>32700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>69800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>68400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>62600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>83700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>60200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>51500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>24800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>54000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>43900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>19500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>28700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-4200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>33900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>37000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-32400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>24200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>29900</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>14300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-12100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>27800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>29900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>17200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>40100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>28800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>43700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>38800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>23700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>51100</v>
       </c>
-      <c r="AQ81" s="3">
+      <c r="AR81" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8993,133 +9191,137 @@
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
       <c r="AQ82" s="3"/>
+      <c r="AR82" s="3"/>
     </row>
-    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E83" s="3">
         <v>46400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>44700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>42500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>40600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>39400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>38500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>36500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>33800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>33100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>31600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>32700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>36700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>35500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>35300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>36600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>37300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>37800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>38500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>39100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>43600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>42300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>44100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>45900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>46600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>47400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>47200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>46300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>45900</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>45500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>44800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>43400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>42400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>42700</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>40200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>37400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>35700</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>34500</v>
       </c>
-      <c r="AQ83" s="3">
+      <c r="AR83" s="3">
         <v>36000</v>
       </c>
     </row>
-    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9243,8 +9445,11 @@
       <c r="AQ84" s="3">
         <v>0</v>
       </c>
+      <c r="AR84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9368,8 +9573,11 @@
       <c r="AQ85" s="3">
         <v>0</v>
       </c>
+      <c r="AR85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9493,8 +9701,11 @@
       <c r="AQ86" s="3">
         <v>0</v>
       </c>
+      <c r="AR86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9618,8 +9829,11 @@
       <c r="AQ87" s="3">
         <v>0</v>
       </c>
+      <c r="AR87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9743,133 +9957,139 @@
       <c r="AQ88" s="3">
         <v>0</v>
       </c>
+      <c r="AR88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>103700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-24600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>419000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>220000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-54000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>328200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>65800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-7500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>325100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-37300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>56300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-85100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>246200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-4500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-12000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-64900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>145500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>104300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>41500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>102400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>111900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>82300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>85200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>191800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-24000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-53600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-56100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>142800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-55500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>12600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>24600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>103700</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>56800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>149900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>42300</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>105800</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-41600</v>
       </c>
-      <c r="AQ89" s="3">
+      <c r="AR89" s="3">
         <v>182500</v>
       </c>
     </row>
-    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9913,133 +10133,137 @@
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
       <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
     </row>
-    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-69500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-70300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-54400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-55200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-79500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-68500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-74600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-65400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-42000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-57400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-67200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-51000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-42900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-65200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-42500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-38400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-43600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-45100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-36700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-20700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-17900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-38200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-45800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-37200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-47300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-46000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-34500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-31800</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-56000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-66000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-58300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-36800</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-40100</v>
       </c>
-      <c r="AQ91" s="3">
+      <c r="AR91" s="3">
         <v>-47300</v>
       </c>
     </row>
-    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -10163,8 +10387,11 @@
       <c r="AQ92" s="3">
         <v>0</v>
       </c>
+      <c r="AR92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10288,133 +10515,139 @@
       <c r="AQ93" s="3">
         <v>0</v>
       </c>
+      <c r="AR93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-291200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-80400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1680500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-47600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-39100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-68600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-59800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-216500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-76700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-42200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-52700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-179900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-40000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-49200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-39100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-33000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-43400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-44100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-35500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-28600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-20400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-18300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-32500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-38400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-33800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-42600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-39100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-45800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-28700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-48100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-59700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-78400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-32900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-38200</v>
       </c>
-      <c r="AQ94" s="3">
+      <c r="AR94" s="3">
         <v>-151600</v>
       </c>
     </row>
-    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10458,8 +10691,9 @@
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
       <c r="AQ95" s="3"/>
+      <c r="AR95" s="3"/>
     </row>
-    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10502,8 +10736,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10583,8 +10817,11 @@
       <c r="AQ96" s="3">
         <v>0</v>
       </c>
+      <c r="AR96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10708,8 +10945,11 @@
       <c r="AQ97" s="3">
         <v>0</v>
       </c>
+      <c r="AR97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10833,8 +11073,11 @@
       <c r="AQ98" s="3">
         <v>0</v>
       </c>
+      <c r="AR98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10958,133 +11201,139 @@
       <c r="AQ99" s="3">
         <v>0</v>
       </c>
+      <c r="AR99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-65400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1860500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-90800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>45900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-191000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>146400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>77700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-187000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>149500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-34100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-24700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-14200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-27200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-55100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-58400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-50400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>305900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-85500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-119000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-701200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>522300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-133200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>37800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>65100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>95700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-6900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-4800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-15500</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-22800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-71000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>25900</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-65100</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>67700</v>
       </c>
-      <c r="AQ100" s="3">
+      <c r="AR100" s="3">
         <v>-16500</v>
       </c>
     </row>
-    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -11127,8 +11376,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -11208,129 +11457,135 @@
       <c r="AQ101" s="3">
         <v>0</v>
       </c>
+      <c r="AR101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:44" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-198700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-170300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>599100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>81600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>12300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-76700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>77400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-4300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-74900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>85400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-67700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>12000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-152800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>158900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-55000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-65300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-125200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>47100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-68700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>318800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-10500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-621300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>589100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>42700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-21000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-95300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>105800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-33400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-26100</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>59500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>19300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-10100</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>7800</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-12100</v>
       </c>
-      <c r="AQ102" s="3">
+      <c r="AR102" s="3">
         <v>14500</v>
       </c>
     </row>
